--- a/SSTSS_GenSim_Modules/Scenario_Selection_Module/catalog_scenarios.xlsx
+++ b/SSTSS_GenSim_Modules/Scenario_Selection_Module/catalog_scenarios.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="442">
   <si>
     <t xml:space="preserve">Category</t>
   </si>
@@ -1036,13 +1036,403 @@
     <t xml:space="preserve">sc67.png</t>
   </si>
   <si>
-    <t xml:space="preserve">SCtes1-S1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tes1</t>
+    <t xml:space="preserve">SCNHTSA-S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Struck Human</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A pedestrian crossing a multi-lane roadway was struck by vehicle. The driver was looking for other vehicles and traffic controls, but did not see the pedestrian. This crash occurs more frequently in urban areas. The weather is typically clear and the road is usually dry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NHTSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Struck Animal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A male driving home after dark on a rural two-lane country road in November struck a deer crossing the road. The driver could not avoid hitting the deer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drowsy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The driver fell asleep and drifted off the right side of the road and struck a telephone pole. Witnesses say that there was no attempt to brake or steer away from the pole. The crash occurred in a rural area at night.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggressive, Departure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The male driver was driving too fast, as well as cutting in and out of traffic, maneuvering the vehicle to the limits of control. The driver lost control of the vehicle and went into a skid. The driver left the roadway and struck the guardrail and then a tree.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slick Road Departure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The driver lost control while driving on an icy, wet road. The driver tried to bring the vehicle back under control by braking and steering. The vehicle spun out and came to rest in the ditch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rough Road Departure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due to the patched and eroded condition of the road surface, the driver lost control of the vehicle and left the roadway.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avoidance, Departure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The driver was alert and driving along a surface street. Suddenly something appeared in the driver's path (e.g., child, bicyclist, or animal). The driver slammed on the brakes and swerved to avoid the immediate threat. The vehicle drove over a curb and into an object.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impaired, Departure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The young (under 25) male driver, who was legally impaired, was driving too fast. He lost control of the vehicle, which left the roadway and overturned. The crash occurred in a rural area between midnight and 2 a.m. on a weekend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Back Into Object</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle A was backing out of a driveway and struck Vehicle B that was parked along the side of the road. Driver A did not see the other vehicle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ran Red “T- Bone”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver ran the red light. The driver saw the light turn yellow but decided to continue through the intersection. The majority of these crashes occur during daylight hours in urban areas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slick Road, Ran Stop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As vehicle approached an intersection, the driver noticed the stop sign, applied the brakes hard, but slid on the wet pavement into crossing traffic. (This group does not include the condition where there is no sign.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inattentive, Ran Stop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An inattentive driver in a vehicle, heading north, did not see a stop sign (two-way only) and struck an eastbound vehicle on the passenger's side.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">View Obstruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A vehicle, at a two-way stop sign, could not see adequately down the road due to the hill. This vehicle pulled out and was struck on the driver's side by a lateral-crossing vehicle. This crash is most likely to occur in daylight in rural areas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Looked but Didn’t See</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle A was turning right at a two-way stop sign. The driver did not see Vehicle B approaching from lateral direction as Vehicle A turned into the lane. Upon turning, Vehicle A was struck by Vehicle B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sirens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A police car, with lights and siren on, slowed to cross through an intersection with a red light. Another vehicle was on the crossing road and did not see the approaching police car.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left Turn Clip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle A, in an attempt to turn left, cut the corner too sharply and clipped Vehicle B waiting at the intersection. Vehicle A began the turn too early and misjudged the distance between cars.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrong Driveway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver A observed Vehicle B approaching with the right turn signal on. A assumed that B was turning into the driveway that A was turning out of and proceeded in front of B. B was not turning until the intersection and struck A in the side.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave to Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From a driveway, Vehicle A was waiting to make a left turn, but full view of all lanes was not possible due to other traffic. Driver B stopped—leaving a gap—and waved driver A through in front of him. However, Driver C was unaware of this arrangement and crashed into the driver's side of Vehicle A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turn into Passer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An impatient driver, A, was following behind a slower vehicle, B. Driver A passed vehicle B. Driver B turned left as A was passing and collided with A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Back into Roadway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver A backed vehicle into roadway. Driver A did not see vehicle B heading west.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tailgate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle B was following Vehicle A too closely. Vehicle A had to stop quickly; B could not stop in time and rear-ended A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distracted, Rear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The driver of Vehicle A was reaching down to retrieve an item from the floor of the vehicle and did not notice that Vehicle B was stopped ahead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avoidance, Rear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle A observed traffic slowing in the curb lane. A decided to change lanes and go around slowing traffic. A changed lanes to the inside lane only to find Vehicle B stopped directly in front. Driver A could not stop and struck B in the rear. (This also includes cases of three cars in the same lane. The middle vehicle pulled out of the lane at the last moment leaving the rear-most vehicle to collide with the foremost.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedal Miss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver A was attempting to stop behind Vehicle B when Driver A's foot missed the brake pedal and Vehicle A struck Vehicle B from behind.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inattentive, Rear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A northbound vehicle, A, was stopped waiting at a red traffic signal in an urban area on a major artery. Another vehicle, B, coming from some distance behind, didn't notice that A was stopped and could not stop in time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stutter Stop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A stopped vehicle, A, was looking left and right down a cross road waiting for traffic to clear before proceeding. Another driver, B, waiting behind A was also checking crossing traffic. Vehicle A started to go, decided that it wasn't safe, and abruptly stopped. Driver B rear-ended A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggressive, Rear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle A was stopped in traffic. Driver B (at a distance from A) was driving too fast. By the time B realized he/she needed to stop, it was not possible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintenance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle A was stopped prior to turning when struck by Vehicle B. Driver B stated that the brakes failed to stop the car. Vehicle B was an older vehicle (more than six years).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slick Road, Rear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle A was braking for stopped traffic. Driver B, coming from some distance behind A, saw the brake lights. When B braked the road was very slick. B did not stop and struck A in the rear.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passing Clip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle A, in an attempt to pass vehicle B, cut around B, but too closely. Driver A misjudged the distance between cars and clipped the corner of B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lane Change Right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver of Vehicle A looked for traffic before changing lanes to the right on a four-lane road. The driver did not see Vehicle B in the curb lane. Vehicle B braked and steered to avoid Vehicle A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visibility, Rear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver A could not see well due to the blowing snow (whiteout conditions). Vehicle B was in front of A and traveling in the same direction. B had to brake for stopped traffic ahead and A did not notice the brake lights.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lane Change Left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver of Vehicle A looked for traffic before changing lanes to the left on a four-lane road. The driver did not see Vehicle B in the next lane. Vehicle B had no time to react and nowhere to go to avoid Vehicle A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lane Change, Rear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle A saw Vehicle B approaching in the next lane. A determined that B was far enough back that A could change lanes. Driver A misjudged the distance and speed of Vehicle B. B could not stop and struck A; Vehicle C also struck B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Back Track Front</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle A stopped too far out in an intersection. Driver A did not see Vehicle B and backed up to allow other traffic through, striking Vehicle B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U-Turn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle A and Vehicle B were both heading in the same direction on a multi-lane road in different lanes. B attempted to turn from the curb lane across the path of A onto a side street. Driver A struck illegally turning B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inexperience, Departure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver A was having a difficult time controlling the vehicle on the slippery road. The driver lost control of the vehicle while starting into a curve and applied the brakes. The vehicle crossed into opposite direction traffic and collided head-on with Vehicle B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impaired, Head-on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A young male driver A, who was legally impaired, was driving too fast. He lost control of the vehicle, crossed the centerline, and struck an approaching vehicle head-on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slick Road, head-on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle A attempted to stop at an intersection, but because of the slick road, lost control. Vehicle B was approaching head-on and was struck by A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run Red Into Left Turner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A northbound vehicle, A, was waiting to make a left turn. The light changed and A began to turn left. A southbound driver, B, accelerated hard, hoping to make the light and struck Vehicle A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Misjudgment, Left Turn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle A was waiting to turn left. Driver A observed B approaching from the opposite direction, but thought there was enough time. Driver A misjudged B’s distance and was struck.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">View Obstructed Left Turn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle A was stopped in the left lane of a four-lane road. Vehicle C was stopped opposite also turning left. Driver A could see only a short distance past C, thought it was clear, and turned. Vehicle B, in curb lane, struck A head-on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miscellaneous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is a miscellaneous assortment that could not be classified as any other previously mentioned crash descriptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCNHTSA-S44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is a crash that may not have occurred without the introduction of a new safety technology. The driver may have used the new technology for increased mobility rather than an increase in safety.</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +1442,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1094,13 +1484,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <name val="Cambria"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1153,7 +1536,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1190,10 +1573,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1215,6 +1594,7 @@
   <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="37.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.53"/>
@@ -1224,8 +1604,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="19.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="18.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="30.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="6.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="11.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="19.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="13.17"/>
@@ -8973,23 +9353,128 @@
         <v>46</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="n">
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="n">
         <v>67</v>
       </c>
+      <c r="B70" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK70" s="1" t="s">
+        <v>312</v>
+      </c>
     </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="9" t="n">
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="n">
         <v>68</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E71" s="1" t="n">
         <v>0</v>
@@ -8997,7 +9482,7 @@
       <c r="F71" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G71" s="1" t="n">
+      <c r="G71" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="1" t="n">
@@ -9031,7 +9516,7 @@
         <v>0</v>
       </c>
       <c r="R71" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71" s="1" t="n">
         <v>0</v>
@@ -9076,18 +9561,4661 @@
         <v>0</v>
       </c>
       <c r="AG71" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH71" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AI71" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK71" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK72" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK73" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK74" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK75" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK76" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK77" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK78" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK79" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK80" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK81" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E82" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK82" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK87" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK88" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK89" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK90" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK91" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK92" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK93" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK95" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK96" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK99" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK100" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK101" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK102" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK103" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK104" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK105" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="E106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK106" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK107" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK108" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK109" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK110" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="E111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK112" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI113" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
